--- a/data/nigeria_messy_sales_dataset.xlsx
+++ b/data/nigeria_messy_sales_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a7ab657c7ad61153/Desktop/Nigeria-Excel-Data-Cleaning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{8ABCDE14-E24E-4FDF-8077-2A7018C4FCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C172CBF-310E-4FE0-8C5A-9B5F0361F41B}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{8ABCDE14-E24E-4FDF-8077-2A7018C4FCD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E1DF698-14B6-4CDF-9A02-75A37BAB649B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4605" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="1096">
   <si>
     <t>Customer Name</t>
   </si>
@@ -3298,6 +3298,21 @@
   </si>
   <si>
     <t>Calculate where possible</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Removed duplicate records</t>
+  </si>
+  <si>
+    <t>No duplicates found</t>
+  </si>
+  <si>
+    <t>Missing names retained because no reliable replacement exists</t>
   </si>
 </sst>
 </file>
@@ -3627,7 +3642,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3742,6 +3757,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3787,23 +3817,29 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -17050,7 +17086,7 @@
   <dimension ref="A1:I551"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="1" max="1" width="23.08984375" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.90625" customWidth="1"/>
@@ -17091,7 +17127,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B2" s="7" t="str">
+      <c r="B2" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -17109,7 +17145,7 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7" t="str">
+      <c r="B3" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -17133,7 +17169,7 @@
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="7" t="str">
+      <c r="B4" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -17154,7 +17190,7 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -17175,7 +17211,7 @@
       <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -17196,7 +17232,7 @@
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -17220,7 +17256,7 @@
       <c r="A8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -17250,7 +17286,7 @@
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="7" t="str">
+      <c r="B9" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -17274,7 +17310,7 @@
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -17298,7 +17334,7 @@
       <c r="A11" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="7" t="str">
+      <c r="B11" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -17322,7 +17358,7 @@
       <c r="A12" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="7" t="str">
+      <c r="B12" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -17343,7 +17379,7 @@
       <c r="A13" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="7" t="str">
+      <c r="B13" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -17373,7 +17409,7 @@
       <c r="A14" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7" t="str">
+      <c r="B14" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -17400,7 +17436,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B15" s="7" t="str">
+      <c r="B15" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -17421,7 +17457,7 @@
       <c r="A16" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="7" t="str">
+      <c r="B16" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -17448,7 +17484,7 @@
       <c r="A17" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="7" t="str">
+      <c r="B17" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -17472,7 +17508,7 @@
       <c r="A18" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="7" t="str">
+      <c r="B18" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -17496,7 +17532,7 @@
       <c r="A19" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="7" t="str">
+      <c r="B19" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -17523,7 +17559,7 @@
       <c r="A20" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="7" t="str">
+      <c r="B20" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -17553,7 +17589,7 @@
       <c r="A21" t="s">
         <v>71</v>
       </c>
-      <c r="B21" s="7" t="str">
+      <c r="B21" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -17583,7 +17619,7 @@
       <c r="A22" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="7" t="str">
+      <c r="B22" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -17604,7 +17640,7 @@
       <c r="A23" t="s">
         <v>75</v>
       </c>
-      <c r="B23" s="7" t="str">
+      <c r="B23" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -17628,7 +17664,7 @@
       <c r="A24" t="s">
         <v>78</v>
       </c>
-      <c r="B24" s="7" t="str">
+      <c r="B24" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -17658,7 +17694,7 @@
       <c r="A25" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="7" t="str">
+      <c r="B25" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -17682,7 +17718,7 @@
       <c r="A26" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="7" t="str">
+      <c r="B26" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -17712,7 +17748,7 @@
       <c r="A27" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="7" t="str">
+      <c r="B27" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -17733,7 +17769,7 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B28" s="7" t="str">
+      <c r="B28" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -17757,7 +17793,7 @@
       <c r="A29" t="s">
         <v>90</v>
       </c>
-      <c r="B29" s="7" t="str">
+      <c r="B29" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -17787,7 +17823,7 @@
       <c r="A30" t="s">
         <v>92</v>
       </c>
-      <c r="B30" s="7" t="str">
+      <c r="B30" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -17808,7 +17844,7 @@
       <c r="A31" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="7" t="str">
+      <c r="B31" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -17838,7 +17874,7 @@
       <c r="A32" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="7" t="str">
+      <c r="B32" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -17859,7 +17895,7 @@
       <c r="A33" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="7" t="str">
+      <c r="B33" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -17889,7 +17925,7 @@
       <c r="A34" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="7" t="str">
+      <c r="B34" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -17919,7 +17955,7 @@
       <c r="A35" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="7" t="str">
+      <c r="B35" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -17943,7 +17979,7 @@
       <c r="A36" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="7" t="str">
+      <c r="B36" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -17967,7 +18003,7 @@
       <c r="A37" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="7" t="str">
+      <c r="B37" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -17991,7 +18027,7 @@
       <c r="A38" t="s">
         <v>111</v>
       </c>
-      <c r="B38" s="7" t="str">
+      <c r="B38" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -18015,7 +18051,7 @@
       <c r="A39" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="7" t="str">
+      <c r="B39" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -18045,7 +18081,7 @@
       <c r="A40" t="s">
         <v>117</v>
       </c>
-      <c r="B40" s="7" t="str">
+      <c r="B40" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -18072,7 +18108,7 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B41" s="7" t="str">
+      <c r="B41" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -18096,7 +18132,7 @@
       <c r="A42" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="7" t="str">
+      <c r="B42" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -18117,7 +18153,7 @@
       <c r="A43" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="7" t="str">
+      <c r="B43" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -18141,7 +18177,7 @@
       <c r="A44" t="s">
         <v>125</v>
       </c>
-      <c r="B44" s="7" t="str">
+      <c r="B44" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -18168,7 +18204,7 @@
       <c r="A45" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="7" t="str">
+      <c r="B45" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -18192,7 +18228,7 @@
       <c r="A46" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="7" t="str">
+      <c r="B46" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -18216,7 +18252,7 @@
       <c r="A47" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="7" t="str">
+      <c r="B47" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -18237,7 +18273,7 @@
       <c r="A48" t="s">
         <v>133</v>
       </c>
-      <c r="B48" s="7" t="str">
+      <c r="B48" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -18258,7 +18294,7 @@
       <c r="A49" t="s">
         <v>135</v>
       </c>
-      <c r="B49" s="7" t="str">
+      <c r="B49" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -18285,7 +18321,7 @@
       <c r="A50" t="s">
         <v>137</v>
       </c>
-      <c r="B50" s="7" t="str">
+      <c r="B50" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -18309,7 +18345,7 @@
       <c r="A51" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="7" t="str">
+      <c r="B51" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -18339,7 +18375,7 @@
       <c r="A52" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="7" t="str">
+      <c r="B52" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -18360,7 +18396,7 @@
       <c r="A53" t="s">
         <v>145</v>
       </c>
-      <c r="B53" s="7" t="str">
+      <c r="B53" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -18381,7 +18417,7 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B54" s="7" t="str">
+      <c r="B54" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -18405,7 +18441,7 @@
       <c r="A55" t="s">
         <v>148</v>
       </c>
-      <c r="B55" s="7" t="str">
+      <c r="B55" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -18426,7 +18462,7 @@
       <c r="A56" t="s">
         <v>150</v>
       </c>
-      <c r="B56" s="7" t="str">
+      <c r="B56" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -18450,7 +18486,7 @@
       <c r="A57" t="s">
         <v>153</v>
       </c>
-      <c r="B57" s="7" t="str">
+      <c r="B57" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -18471,7 +18507,7 @@
       <c r="A58" t="s">
         <v>155</v>
       </c>
-      <c r="B58" s="7" t="str">
+      <c r="B58" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -18489,7 +18525,7 @@
       <c r="A59" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="7" t="str">
+      <c r="B59" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -18513,7 +18549,7 @@
       <c r="A60" t="s">
         <v>158</v>
       </c>
-      <c r="B60" s="7" t="str">
+      <c r="B60" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -18537,7 +18573,7 @@
       <c r="A61" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="7" t="str">
+      <c r="B61" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -18561,7 +18597,7 @@
       <c r="A62" t="s">
         <v>162</v>
       </c>
-      <c r="B62" s="7" t="str">
+      <c r="B62" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -18582,7 +18618,7 @@
       <c r="A63" t="s">
         <v>164</v>
       </c>
-      <c r="B63" s="7" t="str">
+      <c r="B63" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -18612,7 +18648,7 @@
       <c r="A64" t="s">
         <v>166</v>
       </c>
-      <c r="B64" s="7" t="str">
+      <c r="B64" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -18636,7 +18672,7 @@
       <c r="A65" t="s">
         <v>168</v>
       </c>
-      <c r="B65" s="7" t="str">
+      <c r="B65" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -18660,7 +18696,7 @@
       <c r="A66" t="s">
         <v>171</v>
       </c>
-      <c r="B66" s="7" t="str">
+      <c r="B66" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -18678,7 +18714,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B67" s="7" t="str">
+      <c r="B67" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -18702,7 +18738,7 @@
       <c r="A68" t="s">
         <v>175</v>
       </c>
-      <c r="B68" s="7" t="str">
+      <c r="B68" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -18729,7 +18765,7 @@
       <c r="A69" t="s">
         <v>177</v>
       </c>
-      <c r="B69" s="7" t="str">
+      <c r="B69" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -18750,7 +18786,7 @@
       <c r="A70" t="s">
         <v>179</v>
       </c>
-      <c r="B70" s="7" t="str">
+      <c r="B70" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -18774,7 +18810,7 @@
       <c r="A71" t="s">
         <v>181</v>
       </c>
-      <c r="B71" s="7" t="str">
+      <c r="B71" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -18798,7 +18834,7 @@
       <c r="A72" t="s">
         <v>183</v>
       </c>
-      <c r="B72" s="7" t="str">
+      <c r="B72" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -18816,7 +18852,7 @@
       <c r="A73" t="s">
         <v>184</v>
       </c>
-      <c r="B73" s="7" t="str">
+      <c r="B73" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -18846,7 +18882,7 @@
       <c r="A74" t="s">
         <v>186</v>
       </c>
-      <c r="B74" s="7" t="str">
+      <c r="B74" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -18876,7 +18912,7 @@
       <c r="A75" t="s">
         <v>189</v>
       </c>
-      <c r="B75" s="7" t="str">
+      <c r="B75" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -18900,7 +18936,7 @@
       <c r="A76" t="s">
         <v>191</v>
       </c>
-      <c r="B76" s="7" t="str">
+      <c r="B76" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -18924,7 +18960,7 @@
       <c r="A77" t="s">
         <v>193</v>
       </c>
-      <c r="B77" s="7" t="str">
+      <c r="B77" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -18948,7 +18984,7 @@
       <c r="A78" t="s">
         <v>195</v>
       </c>
-      <c r="B78" s="7" t="str">
+      <c r="B78" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -18972,7 +19008,7 @@
       <c r="A79" t="s">
         <v>197</v>
       </c>
-      <c r="B79" s="7" t="str">
+      <c r="B79" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -18993,7 +19029,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B80" s="7" t="str">
+      <c r="B80" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -19017,7 +19053,7 @@
       <c r="A81" t="s">
         <v>200</v>
       </c>
-      <c r="B81" s="7" t="str">
+      <c r="B81" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -19041,7 +19077,7 @@
       <c r="A82" t="s">
         <v>202</v>
       </c>
-      <c r="B82" s="7" t="str">
+      <c r="B82" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -19062,7 +19098,7 @@
       <c r="A83" t="s">
         <v>204</v>
       </c>
-      <c r="B83" s="7" t="str">
+      <c r="B83" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -19086,7 +19122,7 @@
       <c r="A84" t="s">
         <v>207</v>
       </c>
-      <c r="B84" s="7" t="str">
+      <c r="B84" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -19110,7 +19146,7 @@
       <c r="A85" t="s">
         <v>209</v>
       </c>
-      <c r="B85" s="7" t="str">
+      <c r="B85" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -19140,7 +19176,7 @@
       <c r="A86" t="s">
         <v>211</v>
       </c>
-      <c r="B86" s="7" t="str">
+      <c r="B86" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -19161,7 +19197,7 @@
       <c r="A87" t="s">
         <v>212</v>
       </c>
-      <c r="B87" s="7" t="str">
+      <c r="B87" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -19185,7 +19221,7 @@
       <c r="A88" t="s">
         <v>214</v>
       </c>
-      <c r="B88" s="7" t="str">
+      <c r="B88" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -19209,7 +19245,7 @@
       <c r="A89" t="s">
         <v>216</v>
       </c>
-      <c r="B89" s="7" t="str">
+      <c r="B89" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -19239,7 +19275,7 @@
       <c r="A90" t="s">
         <v>218</v>
       </c>
-      <c r="B90" s="7" t="str">
+      <c r="B90" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -19263,7 +19299,7 @@
       <c r="A91" t="s">
         <v>220</v>
       </c>
-      <c r="B91" s="7" t="str">
+      <c r="B91" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -19290,7 +19326,7 @@
       <c r="A92" t="s">
         <v>222</v>
       </c>
-      <c r="B92" s="7" t="str">
+      <c r="B92" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -19305,7 +19341,7 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B93" s="7" t="str">
+      <c r="B93" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -19329,7 +19365,7 @@
       <c r="A94" t="s">
         <v>225</v>
       </c>
-      <c r="B94" s="7" t="str">
+      <c r="B94" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -19353,7 +19389,7 @@
       <c r="A95" t="s">
         <v>227</v>
       </c>
-      <c r="B95" s="7" t="str">
+      <c r="B95" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -19383,7 +19419,7 @@
       <c r="A96" t="s">
         <v>229</v>
       </c>
-      <c r="B96" s="7" t="str">
+      <c r="B96" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -19407,7 +19443,7 @@
       <c r="A97" t="s">
         <v>232</v>
       </c>
-      <c r="B97" s="7" t="str">
+      <c r="B97" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -19431,7 +19467,7 @@
       <c r="A98" t="s">
         <v>234</v>
       </c>
-      <c r="B98" s="7" t="str">
+      <c r="B98" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -19455,7 +19491,7 @@
       <c r="A99" t="s">
         <v>237</v>
       </c>
-      <c r="B99" s="7" t="str">
+      <c r="B99" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -19479,7 +19515,7 @@
       <c r="A100" t="s">
         <v>239</v>
       </c>
-      <c r="B100" s="7" t="str">
+      <c r="B100" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -19500,7 +19536,7 @@
       <c r="A101" t="s">
         <v>240</v>
       </c>
-      <c r="B101" s="7" t="str">
+      <c r="B101" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -19521,7 +19557,7 @@
       <c r="A102" t="s">
         <v>243</v>
       </c>
-      <c r="B102" s="7" t="str">
+      <c r="B102" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -19545,7 +19581,7 @@
       <c r="A103" t="s">
         <v>245</v>
       </c>
-      <c r="B103" s="7" t="str">
+      <c r="B103" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -19569,7 +19605,7 @@
       <c r="A104" t="s">
         <v>247</v>
       </c>
-      <c r="B104" s="7" t="str">
+      <c r="B104" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -19593,7 +19629,7 @@
       <c r="A105" t="s">
         <v>249</v>
       </c>
-      <c r="B105" s="7" t="str">
+      <c r="B105" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -19614,7 +19650,7 @@
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B106" s="7" t="str">
+      <c r="B106" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -19644,7 +19680,7 @@
       <c r="A107" t="s">
         <v>252</v>
       </c>
-      <c r="B107" s="7" t="str">
+      <c r="B107" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -19665,7 +19701,7 @@
       <c r="A108" t="s">
         <v>254</v>
       </c>
-      <c r="B108" s="7" t="str">
+      <c r="B108" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -19689,7 +19725,7 @@
       <c r="A109" t="s">
         <v>256</v>
       </c>
-      <c r="B109" s="7" t="str">
+      <c r="B109" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -19719,7 +19755,7 @@
       <c r="A110" t="s">
         <v>258</v>
       </c>
-      <c r="B110" s="7" t="str">
+      <c r="B110" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -19743,7 +19779,7 @@
       <c r="A111" t="s">
         <v>261</v>
       </c>
-      <c r="B111" s="7" t="str">
+      <c r="B111" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -19770,7 +19806,7 @@
       <c r="A112" t="s">
         <v>263</v>
       </c>
-      <c r="B112" s="7" t="str">
+      <c r="B112" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -19791,7 +19827,7 @@
       <c r="A113" t="s">
         <v>265</v>
       </c>
-      <c r="B113" s="7" t="str">
+      <c r="B113" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -19815,7 +19851,7 @@
       <c r="A114" t="s">
         <v>267</v>
       </c>
-      <c r="B114" s="7" t="str">
+      <c r="B114" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -19836,7 +19872,7 @@
       <c r="A115" t="s">
         <v>268</v>
       </c>
-      <c r="B115" s="7" t="str">
+      <c r="B115" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -19866,7 +19902,7 @@
       <c r="A116" t="s">
         <v>270</v>
       </c>
-      <c r="B116" s="7" t="str">
+      <c r="B116" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -19890,7 +19926,7 @@
       <c r="A117" t="s">
         <v>272</v>
       </c>
-      <c r="B117" s="7" t="str">
+      <c r="B117" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -19914,7 +19950,7 @@
       <c r="A118" t="s">
         <v>274</v>
       </c>
-      <c r="B118" s="7" t="str">
+      <c r="B118" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -19935,7 +19971,7 @@
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B119" s="7" t="str">
+      <c r="B119" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -19965,7 +20001,7 @@
       <c r="A120" t="s">
         <v>278</v>
       </c>
-      <c r="B120" s="7" t="str">
+      <c r="B120" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -19992,7 +20028,7 @@
       <c r="A121" t="s">
         <v>280</v>
       </c>
-      <c r="B121" s="7" t="str">
+      <c r="B121" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -20016,7 +20052,7 @@
       <c r="A122" t="s">
         <v>282</v>
       </c>
-      <c r="B122" s="7" t="str">
+      <c r="B122" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -20037,7 +20073,7 @@
       <c r="A123" t="s">
         <v>284</v>
       </c>
-      <c r="B123" s="7" t="str">
+      <c r="B123" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -20061,7 +20097,7 @@
       <c r="A124" t="s">
         <v>286</v>
       </c>
-      <c r="B124" s="7" t="str">
+      <c r="B124" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -20085,7 +20121,7 @@
       <c r="A125" t="s">
         <v>288</v>
       </c>
-      <c r="B125" s="7" t="str">
+      <c r="B125" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -20109,7 +20145,7 @@
       <c r="A126" t="s">
         <v>290</v>
       </c>
-      <c r="B126" s="7" t="str">
+      <c r="B126" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -20133,7 +20169,7 @@
       <c r="A127" t="s">
         <v>292</v>
       </c>
-      <c r="B127" s="7" t="str">
+      <c r="B127" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -20157,7 +20193,7 @@
       <c r="A128" t="s">
         <v>294</v>
       </c>
-      <c r="B128" s="7" t="str">
+      <c r="B128" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -20175,7 +20211,7 @@
       <c r="A129" t="s">
         <v>295</v>
       </c>
-      <c r="B129" s="7" t="str">
+      <c r="B129" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -20199,7 +20235,7 @@
       <c r="A130" t="s">
         <v>297</v>
       </c>
-      <c r="B130" s="7" t="str">
+      <c r="B130" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -20226,7 +20262,7 @@
       <c r="A131" t="s">
         <v>299</v>
       </c>
-      <c r="B131" s="7" t="str">
+      <c r="B131" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -20244,7 +20280,7 @@
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B132" s="7" t="str">
+      <c r="B132" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -20265,7 +20301,7 @@
       <c r="A133" t="s">
         <v>302</v>
       </c>
-      <c r="B133" s="7" t="str">
+      <c r="B133" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -20286,7 +20322,7 @@
       <c r="A134" t="s">
         <v>304</v>
       </c>
-      <c r="B134" s="7" t="str">
+      <c r="B134" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -20310,7 +20346,7 @@
       <c r="A135" t="s">
         <v>306</v>
       </c>
-      <c r="B135" s="7" t="str">
+      <c r="B135" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -20340,7 +20376,7 @@
       <c r="A136" t="s">
         <v>308</v>
       </c>
-      <c r="B136" s="7" t="str">
+      <c r="B136" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -20364,7 +20400,7 @@
       <c r="A137" t="s">
         <v>310</v>
       </c>
-      <c r="B137" s="7" t="str">
+      <c r="B137" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -20394,7 +20430,7 @@
       <c r="A138" t="s">
         <v>313</v>
       </c>
-      <c r="B138" s="7" t="str">
+      <c r="B138" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -20418,7 +20454,7 @@
       <c r="A139" t="s">
         <v>315</v>
       </c>
-      <c r="B139" s="7" t="str">
+      <c r="B139" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -20448,7 +20484,7 @@
       <c r="A140" t="s">
         <v>317</v>
       </c>
-      <c r="B140" s="7" t="str">
+      <c r="B140" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -20472,7 +20508,7 @@
       <c r="A141" t="s">
         <v>319</v>
       </c>
-      <c r="B141" s="7" t="str">
+      <c r="B141" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -20496,7 +20532,7 @@
       <c r="A142" t="s">
         <v>321</v>
       </c>
-      <c r="B142" s="7" t="str">
+      <c r="B142" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -20517,7 +20553,7 @@
       <c r="A143" t="s">
         <v>322</v>
       </c>
-      <c r="B143" s="7" t="str">
+      <c r="B143" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -20541,7 +20577,7 @@
       <c r="A144" t="s">
         <v>324</v>
       </c>
-      <c r="B144" s="7" t="str">
+      <c r="B144" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -20568,7 +20604,7 @@
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B145" s="7" t="str">
+      <c r="B145" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -20592,7 +20628,7 @@
       <c r="A146" t="s">
         <v>327</v>
       </c>
-      <c r="B146" s="7" t="str">
+      <c r="B146" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -20616,7 +20652,7 @@
       <c r="A147" t="s">
         <v>330</v>
       </c>
-      <c r="B147" s="7" t="str">
+      <c r="B147" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -20640,7 +20676,7 @@
       <c r="A148" t="s">
         <v>332</v>
       </c>
-      <c r="B148" s="7" t="str">
+      <c r="B148" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -20664,7 +20700,7 @@
       <c r="A149" t="s">
         <v>334</v>
       </c>
-      <c r="B149" s="7" t="str">
+      <c r="B149" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -20694,7 +20730,7 @@
       <c r="A150" t="s">
         <v>336</v>
       </c>
-      <c r="B150" s="7" t="str">
+      <c r="B150" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -20718,7 +20754,7 @@
       <c r="A151" t="s">
         <v>338</v>
       </c>
-      <c r="B151" s="7" t="str">
+      <c r="B151" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -20739,7 +20775,7 @@
       <c r="A152" t="s">
         <v>340</v>
       </c>
-      <c r="B152" s="7" t="str">
+      <c r="B152" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -20760,7 +20796,7 @@
       <c r="A153" t="s">
         <v>342</v>
       </c>
-      <c r="B153" s="7" t="str">
+      <c r="B153" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -20781,7 +20817,7 @@
       <c r="A154" t="s">
         <v>344</v>
       </c>
-      <c r="B154" s="7" t="str">
+      <c r="B154" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -20805,7 +20841,7 @@
       <c r="A155" t="s">
         <v>346</v>
       </c>
-      <c r="B155" s="7" t="str">
+      <c r="B155" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -20826,7 +20862,7 @@
       <c r="A156" t="s">
         <v>348</v>
       </c>
-      <c r="B156" s="7" t="str">
+      <c r="B156" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -20844,7 +20880,7 @@
       <c r="A157" t="s">
         <v>349</v>
       </c>
-      <c r="B157" s="7" t="str">
+      <c r="B157" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -20865,7 +20901,7 @@
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B158" s="7" t="str">
+      <c r="B158" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -20886,7 +20922,7 @@
       <c r="A159" t="s">
         <v>352</v>
       </c>
-      <c r="B159" s="7" t="str">
+      <c r="B159" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -20910,7 +20946,7 @@
       <c r="A160" t="s">
         <v>354</v>
       </c>
-      <c r="B160" s="7" t="str">
+      <c r="B160" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -20934,7 +20970,7 @@
       <c r="A161" t="s">
         <v>356</v>
       </c>
-      <c r="B161" s="7" t="str">
+      <c r="B161" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -20955,7 +20991,7 @@
       <c r="A162" t="s">
         <v>358</v>
       </c>
-      <c r="B162" s="7" t="str">
+      <c r="B162" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -20976,7 +21012,7 @@
       <c r="A163" t="s">
         <v>360</v>
       </c>
-      <c r="B163" s="7" t="str">
+      <c r="B163" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -21006,7 +21042,7 @@
       <c r="A164" t="s">
         <v>362</v>
       </c>
-      <c r="B164" s="7" t="str">
+      <c r="B164" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -21030,7 +21066,7 @@
       <c r="A165" t="s">
         <v>365</v>
       </c>
-      <c r="B165" s="7" t="str">
+      <c r="B165" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -21054,7 +21090,7 @@
       <c r="A166" t="s">
         <v>367</v>
       </c>
-      <c r="B166" s="7" t="str">
+      <c r="B166" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -21084,7 +21120,7 @@
       <c r="A167" t="s">
         <v>369</v>
       </c>
-      <c r="B167" s="7" t="str">
+      <c r="B167" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -21108,7 +21144,7 @@
       <c r="A168" t="s">
         <v>371</v>
       </c>
-      <c r="B168" s="7" t="str">
+      <c r="B168" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -21129,7 +21165,7 @@
       <c r="A169" t="s">
         <v>373</v>
       </c>
-      <c r="B169" s="7" t="str">
+      <c r="B169" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -21153,7 +21189,7 @@
       <c r="A170" t="s">
         <v>375</v>
       </c>
-      <c r="B170" s="7" t="str">
+      <c r="B170" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -21174,7 +21210,7 @@
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B171" s="7" t="str">
+      <c r="B171" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -21198,7 +21234,7 @@
       <c r="A172" t="s">
         <v>377</v>
       </c>
-      <c r="B172" s="7" t="str">
+      <c r="B172" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -21222,7 +21258,7 @@
       <c r="A173" t="s">
         <v>379</v>
       </c>
-      <c r="B173" s="7" t="str">
+      <c r="B173" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -21246,7 +21282,7 @@
       <c r="A174" t="s">
         <v>381</v>
       </c>
-      <c r="B174" s="7" t="str">
+      <c r="B174" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -21270,7 +21306,7 @@
       <c r="A175" t="s">
         <v>383</v>
       </c>
-      <c r="B175" s="7" t="str">
+      <c r="B175" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -21294,7 +21330,7 @@
       <c r="A176" t="s">
         <v>385</v>
       </c>
-      <c r="B176" s="7" t="str">
+      <c r="B176" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -21324,7 +21360,7 @@
       <c r="A177" t="s">
         <v>387</v>
       </c>
-      <c r="B177" s="7" t="str">
+      <c r="B177" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -21354,7 +21390,7 @@
       <c r="A178" t="s">
         <v>389</v>
       </c>
-      <c r="B178" s="7" t="str">
+      <c r="B178" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -21378,7 +21414,7 @@
       <c r="A179" t="s">
         <v>391</v>
       </c>
-      <c r="B179" s="7" t="str">
+      <c r="B179" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -21405,7 +21441,7 @@
       <c r="A180" t="s">
         <v>393</v>
       </c>
-      <c r="B180" s="7" t="str">
+      <c r="B180" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -21432,7 +21468,7 @@
       <c r="A181" t="s">
         <v>395</v>
       </c>
-      <c r="B181" s="7" t="str">
+      <c r="B181" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -21453,7 +21489,7 @@
       <c r="A182" t="s">
         <v>397</v>
       </c>
-      <c r="B182" s="7" t="str">
+      <c r="B182" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -21474,7 +21510,7 @@
       <c r="A183" t="s">
         <v>399</v>
       </c>
-      <c r="B183" s="7" t="str">
+      <c r="B183" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -21492,7 +21528,7 @@
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B184" s="7" t="str">
+      <c r="B184" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -21513,7 +21549,7 @@
       <c r="A185" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="7" t="str">
+      <c r="B185" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -21537,7 +21573,7 @@
       <c r="A186" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="7" t="str">
+      <c r="B186" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -21561,7 +21597,7 @@
       <c r="A187" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="7" t="str">
+      <c r="B187" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -21585,7 +21621,7 @@
       <c r="A188" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="7" t="str">
+      <c r="B188" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -21609,7 +21645,7 @@
       <c r="A189" t="s">
         <v>409</v>
       </c>
-      <c r="B189" s="7" t="str">
+      <c r="B189" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -21630,7 +21666,7 @@
       <c r="A190" t="s">
         <v>411</v>
       </c>
-      <c r="B190" s="7" t="str">
+      <c r="B190" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -21651,7 +21687,7 @@
       <c r="A191" t="s">
         <v>413</v>
       </c>
-      <c r="B191" s="7" t="str">
+      <c r="B191" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -21681,7 +21717,7 @@
       <c r="A192" t="s">
         <v>415</v>
       </c>
-      <c r="B192" s="7" t="str">
+      <c r="B192" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -21705,7 +21741,7 @@
       <c r="A193" t="s">
         <v>417</v>
       </c>
-      <c r="B193" s="7" t="str">
+      <c r="B193" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -21729,7 +21765,7 @@
       <c r="A194" t="s">
         <v>419</v>
       </c>
-      <c r="B194" s="7" t="str">
+      <c r="B194" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -21753,7 +21789,7 @@
       <c r="A195" t="s">
         <v>421</v>
       </c>
-      <c r="B195" s="7" t="str">
+      <c r="B195" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -21777,7 +21813,7 @@
       <c r="A196" t="s">
         <v>423</v>
       </c>
-      <c r="B196" s="7" t="str">
+      <c r="B196" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -21798,7 +21834,7 @@
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B197" s="7" t="str">
+      <c r="B197" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -21828,7 +21864,7 @@
       <c r="A198" t="s">
         <v>426</v>
       </c>
-      <c r="B198" s="7" t="str">
+      <c r="B198" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -21849,7 +21885,7 @@
       <c r="A199" t="s">
         <v>427</v>
       </c>
-      <c r="B199" s="7" t="str">
+      <c r="B199" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -21879,7 +21915,7 @@
       <c r="A200" t="s">
         <v>429</v>
       </c>
-      <c r="B200" s="7" t="str">
+      <c r="B200" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -21903,7 +21939,7 @@
       <c r="A201" t="s">
         <v>431</v>
       </c>
-      <c r="B201" s="7" t="str">
+      <c r="B201" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -21933,7 +21969,7 @@
       <c r="A202" t="s">
         <v>433</v>
       </c>
-      <c r="B202" s="7" t="str">
+      <c r="B202" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -21957,7 +21993,7 @@
       <c r="A203" t="s">
         <v>435</v>
       </c>
-      <c r="B203" s="7" t="str">
+      <c r="B203" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -21981,7 +22017,7 @@
       <c r="A204" t="s">
         <v>437</v>
       </c>
-      <c r="B204" s="7" t="str">
+      <c r="B204" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -22005,7 +22041,7 @@
       <c r="A205" t="s">
         <v>439</v>
       </c>
-      <c r="B205" s="7" t="str">
+      <c r="B205" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -22029,7 +22065,7 @@
       <c r="A206" t="s">
         <v>441</v>
       </c>
-      <c r="B206" s="7" t="str">
+      <c r="B206" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -22050,7 +22086,7 @@
       <c r="A207" t="s">
         <v>443</v>
       </c>
-      <c r="B207" s="7" t="str">
+      <c r="B207" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -22074,7 +22110,7 @@
       <c r="A208" t="s">
         <v>445</v>
       </c>
-      <c r="B208" s="7" t="str">
+      <c r="B208" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -22098,7 +22134,7 @@
       <c r="A209" t="s">
         <v>447</v>
       </c>
-      <c r="B209" s="7" t="str">
+      <c r="B209" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -22119,7 +22155,7 @@
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B210" s="7" t="str">
+      <c r="B210" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -22143,7 +22179,7 @@
       <c r="A211" t="s">
         <v>451</v>
       </c>
-      <c r="B211" s="7" t="str">
+      <c r="B211" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -22173,7 +22209,7 @@
       <c r="A212" t="s">
         <v>453</v>
       </c>
-      <c r="B212" s="7" t="str">
+      <c r="B212" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -22191,7 +22227,7 @@
       <c r="A213" t="s">
         <v>454</v>
       </c>
-      <c r="B213" s="7" t="str">
+      <c r="B213" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -22215,7 +22251,7 @@
       <c r="A214" t="s">
         <v>456</v>
       </c>
-      <c r="B214" s="7" t="str">
+      <c r="B214" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -22245,7 +22281,7 @@
       <c r="A215" t="s">
         <v>458</v>
       </c>
-      <c r="B215" s="7" t="str">
+      <c r="B215" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -22269,7 +22305,7 @@
       <c r="A216" t="s">
         <v>460</v>
       </c>
-      <c r="B216" s="7" t="str">
+      <c r="B216" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -22299,7 +22335,7 @@
       <c r="A217" t="s">
         <v>462</v>
       </c>
-      <c r="B217" s="7" t="str">
+      <c r="B217" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -22323,7 +22359,7 @@
       <c r="A218" t="s">
         <v>464</v>
       </c>
-      <c r="B218" s="7" t="str">
+      <c r="B218" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -22347,7 +22383,7 @@
       <c r="A219" t="s">
         <v>467</v>
       </c>
-      <c r="B219" s="7" t="str">
+      <c r="B219" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -22371,7 +22407,7 @@
       <c r="A220" t="s">
         <v>469</v>
       </c>
-      <c r="B220" s="7" t="str">
+      <c r="B220" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -22401,7 +22437,7 @@
       <c r="A221" t="s">
         <v>471</v>
       </c>
-      <c r="B221" s="7" t="str">
+      <c r="B221" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -22425,7 +22461,7 @@
       <c r="A222" t="s">
         <v>473</v>
       </c>
-      <c r="B222" s="7" t="str">
+      <c r="B222" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -22443,7 +22479,7 @@
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B223" s="7" t="str">
+      <c r="B223" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -22464,7 +22500,7 @@
       <c r="A224" t="s">
         <v>476</v>
       </c>
-      <c r="B224" s="7" t="str">
+      <c r="B224" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -22488,7 +22524,7 @@
       <c r="A225" t="s">
         <v>478</v>
       </c>
-      <c r="B225" s="7" t="str">
+      <c r="B225" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -22509,7 +22545,7 @@
       <c r="A226" t="s">
         <v>480</v>
       </c>
-      <c r="B226" s="7" t="str">
+      <c r="B226" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -22530,7 +22566,7 @@
       <c r="A227" t="s">
         <v>481</v>
       </c>
-      <c r="B227" s="7" t="str">
+      <c r="B227" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -22554,7 +22590,7 @@
       <c r="A228" t="s">
         <v>483</v>
       </c>
-      <c r="B228" s="7" t="str">
+      <c r="B228" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -22575,7 +22611,7 @@
       <c r="A229" t="s">
         <v>485</v>
       </c>
-      <c r="B229" s="7" t="str">
+      <c r="B229" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -22599,7 +22635,7 @@
       <c r="A230" t="s">
         <v>487</v>
       </c>
-      <c r="B230" s="7" t="str">
+      <c r="B230" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -22623,7 +22659,7 @@
       <c r="A231" t="s">
         <v>489</v>
       </c>
-      <c r="B231" s="7" t="str">
+      <c r="B231" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -22647,7 +22683,7 @@
       <c r="A232" t="s">
         <v>491</v>
       </c>
-      <c r="B232" s="7" t="str">
+      <c r="B232" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -22671,7 +22707,7 @@
       <c r="A233" t="s">
         <v>493</v>
       </c>
-      <c r="B233" s="7" t="str">
+      <c r="B233" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -22701,7 +22737,7 @@
       <c r="A234" t="s">
         <v>495</v>
       </c>
-      <c r="B234" s="7" t="str">
+      <c r="B234" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -22725,7 +22761,7 @@
       <c r="A235" t="s">
         <v>497</v>
       </c>
-      <c r="B235" s="7" t="str">
+      <c r="B235" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -22746,7 +22782,7 @@
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B236" s="7" t="str">
+      <c r="B236" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -22770,7 +22806,7 @@
       <c r="A237" t="s">
         <v>500</v>
       </c>
-      <c r="B237" s="7" t="str">
+      <c r="B237" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -22794,7 +22830,7 @@
       <c r="A238" t="s">
         <v>502</v>
       </c>
-      <c r="B238" s="7" t="str">
+      <c r="B238" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -22821,7 +22857,7 @@
       <c r="A239" t="s">
         <v>504</v>
       </c>
-      <c r="B239" s="7" t="str">
+      <c r="B239" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -22845,7 +22881,7 @@
       <c r="A240" t="s">
         <v>506</v>
       </c>
-      <c r="B240" s="7" t="str">
+      <c r="B240" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -22866,7 +22902,7 @@
       <c r="A241" t="s">
         <v>507</v>
       </c>
-      <c r="B241" s="7" t="str">
+      <c r="B241" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -22887,7 +22923,7 @@
       <c r="A242" t="s">
         <v>509</v>
       </c>
-      <c r="B242" s="7" t="str">
+      <c r="B242" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -22908,7 +22944,7 @@
       <c r="A243" t="s">
         <v>511</v>
       </c>
-      <c r="B243" s="7" t="str">
+      <c r="B243" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -22932,7 +22968,7 @@
       <c r="A244" t="s">
         <v>513</v>
       </c>
-      <c r="B244" s="7" t="str">
+      <c r="B244" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -22956,7 +22992,7 @@
       <c r="A245" t="s">
         <v>515</v>
       </c>
-      <c r="B245" s="7" t="str">
+      <c r="B245" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -22980,7 +23016,7 @@
       <c r="A246" t="s">
         <v>518</v>
       </c>
-      <c r="B246" s="7" t="str">
+      <c r="B246" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -23004,7 +23040,7 @@
       <c r="A247" t="s">
         <v>520</v>
       </c>
-      <c r="B247" s="7" t="str">
+      <c r="B247" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -23028,7 +23064,7 @@
       <c r="A248" t="s">
         <v>522</v>
       </c>
-      <c r="B248" s="7" t="str">
+      <c r="B248" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -23049,7 +23085,7 @@
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B249" s="7" t="str">
+      <c r="B249" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -23070,7 +23106,7 @@
       <c r="A250" t="s">
         <v>525</v>
       </c>
-      <c r="B250" s="7" t="str">
+      <c r="B250" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -23100,7 +23136,7 @@
       <c r="A251" t="s">
         <v>527</v>
       </c>
-      <c r="B251" s="7" t="str">
+      <c r="B251" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -23121,7 +23157,7 @@
       <c r="A252" t="s">
         <v>529</v>
       </c>
-      <c r="B252" s="7" t="str">
+      <c r="B252" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -23142,7 +23178,7 @@
       <c r="A253" t="s">
         <v>531</v>
       </c>
-      <c r="B253" s="7" t="str">
+      <c r="B253" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -23172,7 +23208,7 @@
       <c r="A254" t="s">
         <v>533</v>
       </c>
-      <c r="B254" s="7" t="str">
+      <c r="B254" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -23199,7 +23235,7 @@
       <c r="A255" t="s">
         <v>534</v>
       </c>
-      <c r="B255" s="7" t="str">
+      <c r="B255" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -23223,7 +23259,7 @@
       <c r="A256" t="s">
         <v>536</v>
       </c>
-      <c r="B256" s="7" t="str">
+      <c r="B256" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -23247,7 +23283,7 @@
       <c r="A257" t="s">
         <v>538</v>
       </c>
-      <c r="B257" s="7" t="str">
+      <c r="B257" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -23271,7 +23307,7 @@
       <c r="A258" t="s">
         <v>540</v>
       </c>
-      <c r="B258" s="7" t="str">
+      <c r="B258" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -23295,7 +23331,7 @@
       <c r="A259" t="s">
         <v>542</v>
       </c>
-      <c r="B259" s="7" t="str">
+      <c r="B259" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -23319,7 +23355,7 @@
       <c r="A260" t="s">
         <v>544</v>
       </c>
-      <c r="B260" s="7" t="str">
+      <c r="B260" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -23340,7 +23376,7 @@
       <c r="A261" t="s">
         <v>546</v>
       </c>
-      <c r="B261" s="7" t="str">
+      <c r="B261" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -23361,7 +23397,7 @@
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B262" s="7" t="str">
+      <c r="B262" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -23382,7 +23418,7 @@
       <c r="A263" t="s">
         <v>549</v>
       </c>
-      <c r="B263" s="7" t="str">
+      <c r="B263" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -23412,7 +23448,7 @@
       <c r="A264" t="s">
         <v>551</v>
       </c>
-      <c r="B264" s="7" t="str">
+      <c r="B264" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -23433,7 +23469,7 @@
       <c r="A265" t="s">
         <v>553</v>
       </c>
-      <c r="B265" s="7" t="str">
+      <c r="B265" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -23457,7 +23493,7 @@
       <c r="A266" t="s">
         <v>555</v>
       </c>
-      <c r="B266" s="7" t="str">
+      <c r="B266" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -23484,7 +23520,7 @@
       <c r="A267" t="s">
         <v>557</v>
       </c>
-      <c r="B267" s="7" t="str">
+      <c r="B267" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -23508,7 +23544,7 @@
       <c r="A268" t="s">
         <v>559</v>
       </c>
-      <c r="B268" s="7" t="str">
+      <c r="B268" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -23529,7 +23565,7 @@
       <c r="A269" t="s">
         <v>560</v>
       </c>
-      <c r="B269" s="7" t="str">
+      <c r="B269" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -23553,7 +23589,7 @@
       <c r="A270" t="s">
         <v>562</v>
       </c>
-      <c r="B270" s="7" t="str">
+      <c r="B270" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -23577,7 +23613,7 @@
       <c r="A271" t="s">
         <v>564</v>
       </c>
-      <c r="B271" s="7" t="str">
+      <c r="B271" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -23598,7 +23634,7 @@
       <c r="A272" t="s">
         <v>566</v>
       </c>
-      <c r="B272" s="7" t="str">
+      <c r="B272" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -23622,7 +23658,7 @@
       <c r="A273" t="s">
         <v>568</v>
       </c>
-      <c r="B273" s="7" t="str">
+      <c r="B273" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -23652,7 +23688,7 @@
       <c r="A274" t="s">
         <v>570</v>
       </c>
-      <c r="B274" s="7" t="str">
+      <c r="B274" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -23670,7 +23706,7 @@
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B275" s="7" t="str">
+      <c r="B275" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -23691,7 +23727,7 @@
       <c r="A276" t="s">
         <v>573</v>
       </c>
-      <c r="B276" s="7" t="str">
+      <c r="B276" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -23715,7 +23751,7 @@
       <c r="A277" t="s">
         <v>575</v>
       </c>
-      <c r="B277" s="7" t="str">
+      <c r="B277" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -23739,7 +23775,7 @@
       <c r="A278" t="s">
         <v>577</v>
       </c>
-      <c r="B278" s="7" t="str">
+      <c r="B278" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -23763,7 +23799,7 @@
       <c r="A279" t="s">
         <v>579</v>
       </c>
-      <c r="B279" s="7" t="str">
+      <c r="B279" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -23787,7 +23823,7 @@
       <c r="A280" t="s">
         <v>581</v>
       </c>
-      <c r="B280" s="7" t="str">
+      <c r="B280" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -23811,7 +23847,7 @@
       <c r="A281" t="s">
         <v>583</v>
       </c>
-      <c r="B281" s="7" t="str">
+      <c r="B281" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -23841,7 +23877,7 @@
       <c r="A282" t="s">
         <v>586</v>
       </c>
-      <c r="B282" s="7" t="str">
+      <c r="B282" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -23859,7 +23895,7 @@
       <c r="A283" t="s">
         <v>587</v>
       </c>
-      <c r="B283" s="7" t="str">
+      <c r="B283" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -23883,7 +23919,7 @@
       <c r="A284" t="s">
         <v>589</v>
       </c>
-      <c r="B284" s="7" t="str">
+      <c r="B284" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -23907,7 +23943,7 @@
       <c r="A285" t="s">
         <v>591</v>
       </c>
-      <c r="B285" s="7" t="str">
+      <c r="B285" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -23931,7 +23967,7 @@
       <c r="A286" t="s">
         <v>593</v>
       </c>
-      <c r="B286" s="7" t="str">
+      <c r="B286" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -23958,7 +23994,7 @@
       <c r="A287" t="s">
         <v>595</v>
       </c>
-      <c r="B287" s="7" t="str">
+      <c r="B287" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -23979,7 +24015,7 @@
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B288" s="7" t="str">
+      <c r="B288" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -24003,7 +24039,7 @@
       <c r="A289" t="s">
         <v>598</v>
       </c>
-      <c r="B289" s="7" t="str">
+      <c r="B289" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -24030,7 +24066,7 @@
       <c r="A290" t="s">
         <v>600</v>
       </c>
-      <c r="B290" s="7" t="str">
+      <c r="B290" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -24054,7 +24090,7 @@
       <c r="A291" t="s">
         <v>602</v>
       </c>
-      <c r="B291" s="7" t="str">
+      <c r="B291" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -24081,7 +24117,7 @@
       <c r="A292" t="s">
         <v>604</v>
       </c>
-      <c r="B292" s="7" t="str">
+      <c r="B292" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -24105,7 +24141,7 @@
       <c r="A293" t="s">
         <v>606</v>
       </c>
-      <c r="B293" s="7" t="str">
+      <c r="B293" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -24129,7 +24165,7 @@
       <c r="A294" t="s">
         <v>608</v>
       </c>
-      <c r="B294" s="7" t="str">
+      <c r="B294" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -24159,7 +24195,7 @@
       <c r="A295" t="s">
         <v>610</v>
       </c>
-      <c r="B295" s="7" t="str">
+      <c r="B295" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -24189,7 +24225,7 @@
       <c r="A296" t="s">
         <v>612</v>
       </c>
-      <c r="B296" s="7" t="str">
+      <c r="B296" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -24207,7 +24243,7 @@
       <c r="A297" t="s">
         <v>613</v>
       </c>
-      <c r="B297" s="7" t="str">
+      <c r="B297" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -24237,7 +24273,7 @@
       <c r="A298" t="s">
         <v>615</v>
       </c>
-      <c r="B298" s="7" t="str">
+      <c r="B298" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -24264,7 +24300,7 @@
       <c r="A299" t="s">
         <v>617</v>
       </c>
-      <c r="B299" s="7" t="str">
+      <c r="B299" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -24294,7 +24330,7 @@
       <c r="A300" t="s">
         <v>515</v>
       </c>
-      <c r="B300" s="7" t="str">
+      <c r="B300" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -24315,7 +24351,7 @@
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B301" s="7" t="str">
+      <c r="B301" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -24339,7 +24375,7 @@
       <c r="A302" t="s">
         <v>621</v>
       </c>
-      <c r="B302" s="7" t="str">
+      <c r="B302" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -24360,7 +24396,7 @@
       <c r="A303" t="s">
         <v>623</v>
       </c>
-      <c r="B303" s="7" t="str">
+      <c r="B303" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -24390,7 +24426,7 @@
       <c r="A304" t="s">
         <v>625</v>
       </c>
-      <c r="B304" s="7" t="str">
+      <c r="B304" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -24414,7 +24450,7 @@
       <c r="A305" t="s">
         <v>627</v>
       </c>
-      <c r="B305" s="7" t="str">
+      <c r="B305" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -24438,7 +24474,7 @@
       <c r="A306" t="s">
         <v>629</v>
       </c>
-      <c r="B306" s="7" t="str">
+      <c r="B306" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -24459,7 +24495,7 @@
       <c r="A307" t="s">
         <v>631</v>
       </c>
-      <c r="B307" s="7" t="str">
+      <c r="B307" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -24483,7 +24519,7 @@
       <c r="A308" t="s">
         <v>633</v>
       </c>
-      <c r="B308" s="7" t="str">
+      <c r="B308" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -24513,7 +24549,7 @@
       <c r="A309" t="s">
         <v>635</v>
       </c>
-      <c r="B309" s="7" t="str">
+      <c r="B309" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -24543,7 +24579,7 @@
       <c r="A310" t="s">
         <v>637</v>
       </c>
-      <c r="B310" s="7" t="str">
+      <c r="B310" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -24570,7 +24606,7 @@
       <c r="A311" t="s">
         <v>638</v>
       </c>
-      <c r="B311" s="7" t="str">
+      <c r="B311" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -24594,7 +24630,7 @@
       <c r="A312" t="s">
         <v>640</v>
       </c>
-      <c r="B312" s="7" t="str">
+      <c r="B312" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -24615,7 +24651,7 @@
       <c r="A313" t="s">
         <v>642</v>
       </c>
-      <c r="B313" s="7" t="str">
+      <c r="B313" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -24636,7 +24672,7 @@
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B314" s="7" t="str">
+      <c r="B314" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -24657,7 +24693,7 @@
       <c r="A315" t="s">
         <v>645</v>
       </c>
-      <c r="B315" s="7" t="str">
+      <c r="B315" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -24678,7 +24714,7 @@
       <c r="A316" t="s">
         <v>647</v>
       </c>
-      <c r="B316" s="7" t="str">
+      <c r="B316" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -24708,7 +24744,7 @@
       <c r="A317" t="s">
         <v>649</v>
       </c>
-      <c r="B317" s="7" t="str">
+      <c r="B317" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -24732,7 +24768,7 @@
       <c r="A318" t="s">
         <v>651</v>
       </c>
-      <c r="B318" s="7" t="str">
+      <c r="B318" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -24756,7 +24792,7 @@
       <c r="A319" t="s">
         <v>653</v>
       </c>
-      <c r="B319" s="7" t="str">
+      <c r="B319" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -24786,7 +24822,7 @@
       <c r="A320" t="s">
         <v>655</v>
       </c>
-      <c r="B320" s="7" t="str">
+      <c r="B320" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -24810,7 +24846,7 @@
       <c r="A321" t="s">
         <v>657</v>
       </c>
-      <c r="B321" s="7" t="str">
+      <c r="B321" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -24834,7 +24870,7 @@
       <c r="A322" t="s">
         <v>659</v>
       </c>
-      <c r="B322" s="7" t="str">
+      <c r="B322" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -24855,7 +24891,7 @@
       <c r="A323" t="s">
         <v>661</v>
       </c>
-      <c r="B323" s="7" t="str">
+      <c r="B323" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -24879,7 +24915,7 @@
       <c r="A324" t="s">
         <v>663</v>
       </c>
-      <c r="B324" s="7" t="str">
+      <c r="B324" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -24897,7 +24933,7 @@
       <c r="A325" t="s">
         <v>664</v>
       </c>
-      <c r="B325" s="7" t="str">
+      <c r="B325" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -24921,7 +24957,7 @@
       <c r="A326" t="s">
         <v>666</v>
       </c>
-      <c r="B326" s="7" t="str">
+      <c r="B326" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -24948,7 +24984,7 @@
       </c>
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B327" s="7" t="str">
+      <c r="B327" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -24972,7 +25008,7 @@
       <c r="A328" t="s">
         <v>669</v>
       </c>
-      <c r="B328" s="7" t="str">
+      <c r="B328" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -24996,7 +25032,7 @@
       <c r="A329" t="s">
         <v>671</v>
       </c>
-      <c r="B329" s="7" t="str">
+      <c r="B329" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -25026,7 +25062,7 @@
       <c r="A330" t="s">
         <v>673</v>
       </c>
-      <c r="B330" s="7" t="str">
+      <c r="B330" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -25050,7 +25086,7 @@
       <c r="A331" t="s">
         <v>675</v>
       </c>
-      <c r="B331" s="7" t="str">
+      <c r="B331" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -25071,7 +25107,7 @@
       <c r="A332" t="s">
         <v>677</v>
       </c>
-      <c r="B332" s="7" t="str">
+      <c r="B332" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -25095,7 +25131,7 @@
       <c r="A333" t="s">
         <v>679</v>
       </c>
-      <c r="B333" s="7" t="str">
+      <c r="B333" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -25119,7 +25155,7 @@
       <c r="A334" t="s">
         <v>681</v>
       </c>
-      <c r="B334" s="7" t="str">
+      <c r="B334" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -25143,7 +25179,7 @@
       <c r="A335" t="s">
         <v>683</v>
       </c>
-      <c r="B335" s="7" t="str">
+      <c r="B335" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -25170,7 +25206,7 @@
       <c r="A336" t="s">
         <v>685</v>
       </c>
-      <c r="B336" s="7" t="str">
+      <c r="B336" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -25194,7 +25230,7 @@
       <c r="A337" t="s">
         <v>687</v>
       </c>
-      <c r="B337" s="7" t="str">
+      <c r="B337" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -25215,7 +25251,7 @@
       <c r="A338" t="s">
         <v>689</v>
       </c>
-      <c r="B338" s="7" t="str">
+      <c r="B338" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -25233,7 +25269,7 @@
       <c r="A339" t="s">
         <v>690</v>
       </c>
-      <c r="B339" s="7" t="str">
+      <c r="B339" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -25254,7 +25290,7 @@
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B340" s="7" t="str">
+      <c r="B340" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -25275,7 +25311,7 @@
       <c r="A341" t="s">
         <v>693</v>
       </c>
-      <c r="B341" s="7" t="str">
+      <c r="B341" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -25299,7 +25335,7 @@
       <c r="A342" t="s">
         <v>695</v>
       </c>
-      <c r="B342" s="7" t="str">
+      <c r="B342" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -25320,7 +25356,7 @@
       <c r="A343" t="s">
         <v>697</v>
       </c>
-      <c r="B343" s="7" t="str">
+      <c r="B343" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -25341,7 +25377,7 @@
       <c r="A344" t="s">
         <v>699</v>
       </c>
-      <c r="B344" s="7" t="str">
+      <c r="B344" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -25365,7 +25401,7 @@
       <c r="A345" t="s">
         <v>701</v>
       </c>
-      <c r="B345" s="7" t="str">
+      <c r="B345" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -25386,7 +25422,7 @@
       <c r="A346" t="s">
         <v>703</v>
       </c>
-      <c r="B346" s="7" t="str">
+      <c r="B346" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -25416,7 +25452,7 @@
       <c r="A347" t="s">
         <v>705</v>
       </c>
-      <c r="B347" s="7" t="str">
+      <c r="B347" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -25440,7 +25476,7 @@
       <c r="A348" t="s">
         <v>707</v>
       </c>
-      <c r="B348" s="7" t="str">
+      <c r="B348" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -25461,7 +25497,7 @@
       <c r="A349" t="s">
         <v>709</v>
       </c>
-      <c r="B349" s="7" t="str">
+      <c r="B349" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -25485,7 +25521,7 @@
       <c r="A350" t="s">
         <v>711</v>
       </c>
-      <c r="B350" s="7" t="str">
+      <c r="B350" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -25509,7 +25545,7 @@
       <c r="A351" t="s">
         <v>713</v>
       </c>
-      <c r="B351" s="7" t="str">
+      <c r="B351" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -25533,7 +25569,7 @@
       <c r="A352" t="s">
         <v>715</v>
       </c>
-      <c r="B352" s="7" t="str">
+      <c r="B352" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -25551,7 +25587,7 @@
       </c>
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B353" s="7" t="str">
+      <c r="B353" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -25575,7 +25611,7 @@
       <c r="A354" t="s">
         <v>717</v>
       </c>
-      <c r="B354" s="7" t="str">
+      <c r="B354" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -25599,7 +25635,7 @@
       <c r="A355" t="s">
         <v>719</v>
       </c>
-      <c r="B355" s="7" t="str">
+      <c r="B355" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -25623,7 +25659,7 @@
       <c r="A356" t="s">
         <v>721</v>
       </c>
-      <c r="B356" s="7" t="str">
+      <c r="B356" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -25653,7 +25689,7 @@
       <c r="A357" t="s">
         <v>723</v>
       </c>
-      <c r="B357" s="7" t="str">
+      <c r="B357" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -25683,7 +25719,7 @@
       <c r="A358" t="s">
         <v>725</v>
       </c>
-      <c r="B358" s="7" t="str">
+      <c r="B358" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -25707,7 +25743,7 @@
       <c r="A359" t="s">
         <v>727</v>
       </c>
-      <c r="B359" s="7" t="str">
+      <c r="B359" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -25731,7 +25767,7 @@
       <c r="A360" t="s">
         <v>729</v>
       </c>
-      <c r="B360" s="7" t="str">
+      <c r="B360" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -25755,7 +25791,7 @@
       <c r="A361" t="s">
         <v>731</v>
       </c>
-      <c r="B361" s="7" t="str">
+      <c r="B361" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -25785,7 +25821,7 @@
       <c r="A362" t="s">
         <v>733</v>
       </c>
-      <c r="B362" s="7" t="str">
+      <c r="B362" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -25806,7 +25842,7 @@
       <c r="A363" t="s">
         <v>735</v>
       </c>
-      <c r="B363" s="7" t="str">
+      <c r="B363" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -25827,7 +25863,7 @@
       <c r="A364" t="s">
         <v>737</v>
       </c>
-      <c r="B364" s="7" t="str">
+      <c r="B364" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -25857,7 +25893,7 @@
       <c r="A365" t="s">
         <v>739</v>
       </c>
-      <c r="B365" s="7" t="str">
+      <c r="B365" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -25875,7 +25911,7 @@
       </c>
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B366" s="7" t="str">
+      <c r="B366" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -25902,7 +25938,7 @@
       <c r="A367" t="s">
         <v>741</v>
       </c>
-      <c r="B367" s="7" t="str">
+      <c r="B367" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -25926,7 +25962,7 @@
       <c r="A368" t="s">
         <v>743</v>
       </c>
-      <c r="B368" s="7" t="str">
+      <c r="B368" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -25947,7 +25983,7 @@
       <c r="A369" t="s">
         <v>745</v>
       </c>
-      <c r="B369" s="7" t="str">
+      <c r="B369" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -25971,7 +26007,7 @@
       <c r="A370" t="s">
         <v>747</v>
       </c>
-      <c r="B370" s="7" t="str">
+      <c r="B370" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -26001,7 +26037,7 @@
       <c r="A371" t="s">
         <v>749</v>
       </c>
-      <c r="B371" s="7" t="str">
+      <c r="B371" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -26025,7 +26061,7 @@
       <c r="A372" t="s">
         <v>751</v>
       </c>
-      <c r="B372" s="7" t="str">
+      <c r="B372" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -26046,7 +26082,7 @@
       <c r="A373" t="s">
         <v>753</v>
       </c>
-      <c r="B373" s="7" t="str">
+      <c r="B373" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -26067,7 +26103,7 @@
       <c r="A374" t="s">
         <v>755</v>
       </c>
-      <c r="B374" s="7" t="str">
+      <c r="B374" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -26091,7 +26127,7 @@
       <c r="A375" t="s">
         <v>757</v>
       </c>
-      <c r="B375" s="7" t="str">
+      <c r="B375" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -26118,7 +26154,7 @@
       <c r="A376" t="s">
         <v>759</v>
       </c>
-      <c r="B376" s="7" t="str">
+      <c r="B376" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -26142,7 +26178,7 @@
       <c r="A377" t="s">
         <v>761</v>
       </c>
-      <c r="B377" s="7" t="str">
+      <c r="B377" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -26163,7 +26199,7 @@
       <c r="A378" t="s">
         <v>763</v>
       </c>
-      <c r="B378" s="7" t="str">
+      <c r="B378" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -26181,7 +26217,7 @@
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B379" s="7" t="str">
+      <c r="B379" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -26211,7 +26247,7 @@
       <c r="A380" t="s">
         <v>766</v>
       </c>
-      <c r="B380" s="7" t="str">
+      <c r="B380" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -26232,7 +26268,7 @@
       <c r="A381" t="s">
         <v>767</v>
       </c>
-      <c r="B381" s="7" t="str">
+      <c r="B381" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -26256,7 +26292,7 @@
       <c r="A382" t="s">
         <v>769</v>
       </c>
-      <c r="B382" s="7" t="str">
+      <c r="B382" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -26277,7 +26313,7 @@
       <c r="A383" t="s">
         <v>771</v>
       </c>
-      <c r="B383" s="7" t="str">
+      <c r="B383" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -26298,7 +26334,7 @@
       <c r="A384" t="s">
         <v>773</v>
       </c>
-      <c r="B384" s="7" t="str">
+      <c r="B384" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -26322,7 +26358,7 @@
       <c r="A385" t="s">
         <v>775</v>
       </c>
-      <c r="B385" s="7" t="str">
+      <c r="B385" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -26343,7 +26379,7 @@
       <c r="A386" t="s">
         <v>777</v>
       </c>
-      <c r="B386" s="7" t="str">
+      <c r="B386" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -26373,7 +26409,7 @@
       <c r="A387" t="s">
         <v>779</v>
       </c>
-      <c r="B387" s="7" t="str">
+      <c r="B387" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -26397,7 +26433,7 @@
       <c r="A388" t="s">
         <v>781</v>
       </c>
-      <c r="B388" s="7" t="str">
+      <c r="B388" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -26421,7 +26457,7 @@
       <c r="A389" t="s">
         <v>783</v>
       </c>
-      <c r="B389" s="7" t="str">
+      <c r="B389" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -26445,7 +26481,7 @@
       <c r="A390" t="s">
         <v>785</v>
       </c>
-      <c r="B390" s="7" t="str">
+      <c r="B390" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -26475,7 +26511,7 @@
       <c r="A391" t="s">
         <v>787</v>
       </c>
-      <c r="B391" s="7" t="str">
+      <c r="B391" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -26496,7 +26532,7 @@
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B392" s="7" t="str">
+      <c r="B392" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -26517,7 +26553,7 @@
       <c r="A393" t="s">
         <v>790</v>
       </c>
-      <c r="B393" s="7" t="str">
+      <c r="B393" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -26541,7 +26577,7 @@
       <c r="A394" t="s">
         <v>792</v>
       </c>
-      <c r="B394" s="7" t="str">
+      <c r="B394" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -26568,7 +26604,7 @@
       <c r="A395" t="s">
         <v>793</v>
       </c>
-      <c r="B395" s="7" t="str">
+      <c r="B395" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -26598,7 +26634,7 @@
       <c r="A396" t="s">
         <v>795</v>
       </c>
-      <c r="B396" s="7" t="str">
+      <c r="B396" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -26622,7 +26658,7 @@
       <c r="A397" t="s">
         <v>797</v>
       </c>
-      <c r="B397" s="7" t="str">
+      <c r="B397" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -26652,7 +26688,7 @@
       <c r="A398" t="s">
         <v>799</v>
       </c>
-      <c r="B398" s="7" t="str">
+      <c r="B398" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -26682,7 +26718,7 @@
       <c r="A399" t="s">
         <v>801</v>
       </c>
-      <c r="B399" s="7" t="str">
+      <c r="B399" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -26706,7 +26742,7 @@
       <c r="A400" t="s">
         <v>803</v>
       </c>
-      <c r="B400" s="7" t="str">
+      <c r="B400" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -26727,7 +26763,7 @@
       <c r="A401" t="s">
         <v>805</v>
       </c>
-      <c r="B401" s="7" t="str">
+      <c r="B401" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -26751,7 +26787,7 @@
       <c r="A402" t="s">
         <v>807</v>
       </c>
-      <c r="B402" s="7" t="str">
+      <c r="B402" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -26772,7 +26808,7 @@
       <c r="A403" t="s">
         <v>809</v>
       </c>
-      <c r="B403" s="7" t="str">
+      <c r="B403" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -26796,7 +26832,7 @@
       <c r="A404" t="s">
         <v>811</v>
       </c>
-      <c r="B404" s="7" t="str">
+      <c r="B404" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -26817,7 +26853,7 @@
       </c>
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B405" s="7" t="str">
+      <c r="B405" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -26841,7 +26877,7 @@
       <c r="A406" t="s">
         <v>814</v>
       </c>
-      <c r="B406" s="7" t="str">
+      <c r="B406" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -26871,7 +26907,7 @@
       <c r="A407" t="s">
         <v>816</v>
       </c>
-      <c r="B407" s="7" t="str">
+      <c r="B407" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -26901,7 +26937,7 @@
       <c r="A408" t="s">
         <v>818</v>
       </c>
-      <c r="B408" s="7" t="str">
+      <c r="B408" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -26919,7 +26955,7 @@
       <c r="A409" t="s">
         <v>819</v>
       </c>
-      <c r="B409" s="7" t="str">
+      <c r="B409" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -26943,7 +26979,7 @@
       <c r="A410" t="s">
         <v>821</v>
       </c>
-      <c r="B410" s="7" t="str">
+      <c r="B410" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -26967,7 +27003,7 @@
       <c r="A411" t="s">
         <v>823</v>
       </c>
-      <c r="B411" s="7" t="str">
+      <c r="B411" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -26997,7 +27033,7 @@
       <c r="A412" t="s">
         <v>825</v>
       </c>
-      <c r="B412" s="7" t="str">
+      <c r="B412" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -27018,7 +27054,7 @@
       <c r="A413" t="s">
         <v>827</v>
       </c>
-      <c r="B413" s="7" t="str">
+      <c r="B413" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -27042,7 +27078,7 @@
       <c r="A414" t="s">
         <v>829</v>
       </c>
-      <c r="B414" s="7" t="str">
+      <c r="B414" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -27063,7 +27099,7 @@
       <c r="A415" t="s">
         <v>831</v>
       </c>
-      <c r="B415" s="7" t="str">
+      <c r="B415" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -27093,7 +27129,7 @@
       <c r="A416" t="s">
         <v>833</v>
       </c>
-      <c r="B416" s="7" t="str">
+      <c r="B416" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -27117,7 +27153,7 @@
       <c r="A417" t="s">
         <v>835</v>
       </c>
-      <c r="B417" s="7" t="str">
+      <c r="B417" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -27138,7 +27174,7 @@
       </c>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B418" s="7" t="str">
+      <c r="B418" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -27162,7 +27198,7 @@
       <c r="A419" t="s">
         <v>838</v>
       </c>
-      <c r="B419" s="7" t="str">
+      <c r="B419" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -27186,7 +27222,7 @@
       <c r="A420" t="s">
         <v>840</v>
       </c>
-      <c r="B420" s="7" t="str">
+      <c r="B420" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -27213,7 +27249,7 @@
       <c r="A421" t="s">
         <v>842</v>
       </c>
-      <c r="B421" s="7" t="str">
+      <c r="B421" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -27243,7 +27279,7 @@
       <c r="A422" t="s">
         <v>844</v>
       </c>
-      <c r="B422" s="7" t="str">
+      <c r="B422" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -27261,7 +27297,7 @@
       <c r="A423" t="s">
         <v>845</v>
       </c>
-      <c r="B423" s="7" t="str">
+      <c r="B423" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -27285,7 +27321,7 @@
       <c r="A424" t="s">
         <v>847</v>
       </c>
-      <c r="B424" s="7" t="str">
+      <c r="B424" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -27315,7 +27351,7 @@
       <c r="A425" t="s">
         <v>849</v>
       </c>
-      <c r="B425" s="7" t="str">
+      <c r="B425" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -27339,7 +27375,7 @@
       <c r="A426" t="s">
         <v>851</v>
       </c>
-      <c r="B426" s="7" t="str">
+      <c r="B426" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -27363,7 +27399,7 @@
       <c r="A427" t="s">
         <v>853</v>
       </c>
-      <c r="B427" s="7" t="str">
+      <c r="B427" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -27393,7 +27429,7 @@
       <c r="A428" t="s">
         <v>855</v>
       </c>
-      <c r="B428" s="7" t="str">
+      <c r="B428" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -27417,7 +27453,7 @@
       <c r="A429" t="s">
         <v>857</v>
       </c>
-      <c r="B429" s="7" t="str">
+      <c r="B429" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -27441,7 +27477,7 @@
       <c r="A430" t="s">
         <v>859</v>
       </c>
-      <c r="B430" s="7" t="str">
+      <c r="B430" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -27459,7 +27495,7 @@
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B431" s="7" t="str">
+      <c r="B431" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -27480,7 +27516,7 @@
       <c r="A432" t="s">
         <v>862</v>
       </c>
-      <c r="B432" s="7" t="str">
+      <c r="B432" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -27504,7 +27540,7 @@
       <c r="A433" t="s">
         <v>864</v>
       </c>
-      <c r="B433" s="7" t="str">
+      <c r="B433" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -27525,7 +27561,7 @@
       <c r="A434" t="s">
         <v>866</v>
       </c>
-      <c r="B434" s="7" t="str">
+      <c r="B434" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -27555,7 +27591,7 @@
       <c r="A435" t="s">
         <v>869</v>
       </c>
-      <c r="B435" s="7" t="str">
+      <c r="B435" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -27585,7 +27621,7 @@
       <c r="A436" t="s">
         <v>871</v>
       </c>
-      <c r="B436" s="7" t="str">
+      <c r="B436" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -27606,7 +27642,7 @@
       <c r="A437" t="s">
         <v>872</v>
       </c>
-      <c r="B437" s="7" t="str">
+      <c r="B437" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -27630,7 +27666,7 @@
       <c r="A438" t="s">
         <v>874</v>
       </c>
-      <c r="B438" s="7" t="str">
+      <c r="B438" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -27654,7 +27690,7 @@
       <c r="A439" t="s">
         <v>876</v>
       </c>
-      <c r="B439" s="7" t="str">
+      <c r="B439" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -27678,7 +27714,7 @@
       <c r="A440" t="s">
         <v>878</v>
       </c>
-      <c r="B440" s="7" t="str">
+      <c r="B440" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -27708,7 +27744,7 @@
       <c r="A441" t="s">
         <v>880</v>
       </c>
-      <c r="B441" s="7" t="str">
+      <c r="B441" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -27738,7 +27774,7 @@
       <c r="A442" t="s">
         <v>882</v>
       </c>
-      <c r="B442" s="7" t="str">
+      <c r="B442" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -27759,7 +27795,7 @@
       <c r="A443" t="s">
         <v>884</v>
       </c>
-      <c r="B443" s="7" t="str">
+      <c r="B443" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -27780,7 +27816,7 @@
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B444" s="7" t="str">
+      <c r="B444" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -27804,7 +27840,7 @@
       <c r="A445" t="s">
         <v>887</v>
       </c>
-      <c r="B445" s="7" t="str">
+      <c r="B445" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -27828,7 +27864,7 @@
       <c r="A446" t="s">
         <v>889</v>
       </c>
-      <c r="B446" s="7" t="str">
+      <c r="B446" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -27852,7 +27888,7 @@
       <c r="A447" t="s">
         <v>891</v>
       </c>
-      <c r="B447" s="7" t="str">
+      <c r="B447" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -27882,7 +27918,7 @@
       <c r="A448" t="s">
         <v>893</v>
       </c>
-      <c r="B448" s="7" t="str">
+      <c r="B448" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -27906,7 +27942,7 @@
       <c r="A449" t="s">
         <v>895</v>
       </c>
-      <c r="B449" s="7" t="str">
+      <c r="B449" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -27936,7 +27972,7 @@
       <c r="A450" t="s">
         <v>897</v>
       </c>
-      <c r="B450" s="7" t="str">
+      <c r="B450" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -27957,7 +27993,7 @@
       <c r="A451" t="s">
         <v>898</v>
       </c>
-      <c r="B451" s="7" t="str">
+      <c r="B451" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -27981,7 +28017,7 @@
       <c r="A452" t="s">
         <v>900</v>
       </c>
-      <c r="B452" s="7" t="str">
+      <c r="B452" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -28005,7 +28041,7 @@
       <c r="A453" t="s">
         <v>902</v>
       </c>
-      <c r="B453" s="7" t="str">
+      <c r="B453" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -28029,7 +28065,7 @@
       <c r="A454" t="s">
         <v>904</v>
       </c>
-      <c r="B454" s="7" t="str">
+      <c r="B454" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -28053,7 +28089,7 @@
       <c r="A455" t="s">
         <v>906</v>
       </c>
-      <c r="B455" s="7" t="str">
+      <c r="B455" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -28083,7 +28119,7 @@
       <c r="A456" t="s">
         <v>908</v>
       </c>
-      <c r="B456" s="7" t="str">
+      <c r="B456" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Anambra</v>
       </c>
@@ -28104,7 +28140,7 @@
       </c>
     </row>
     <row r="457" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B457" s="7" t="str">
+      <c r="B457" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -28134,7 +28170,7 @@
       <c r="A458" t="s">
         <v>911</v>
       </c>
-      <c r="B458" s="7" t="str">
+      <c r="B458" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -28164,7 +28200,7 @@
       <c r="A459" t="s">
         <v>913</v>
       </c>
-      <c r="B459" s="7" t="str">
+      <c r="B459" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -28194,7 +28230,7 @@
       <c r="A460" t="s">
         <v>915</v>
       </c>
-      <c r="B460" s="7" t="str">
+      <c r="B460" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -28218,7 +28254,7 @@
       <c r="A461" t="s">
         <v>917</v>
       </c>
-      <c r="B461" s="7" t="str">
+      <c r="B461" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -28248,7 +28284,7 @@
       <c r="A462" t="s">
         <v>919</v>
       </c>
-      <c r="B462" s="7" t="str">
+      <c r="B462" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -28269,7 +28305,7 @@
       <c r="A463" t="s">
         <v>921</v>
       </c>
-      <c r="B463" s="7" t="str">
+      <c r="B463" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Osun</v>
       </c>
@@ -28299,7 +28335,7 @@
       <c r="A464" t="s">
         <v>923</v>
       </c>
-      <c r="B464" s="7" t="str">
+      <c r="B464" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -28326,7 +28362,7 @@
       <c r="A465" t="s">
         <v>924</v>
       </c>
-      <c r="B465" s="7" t="str">
+      <c r="B465" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -28350,7 +28386,7 @@
       <c r="A466" t="s">
         <v>926</v>
       </c>
-      <c r="B466" s="7" t="str">
+      <c r="B466" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -28380,7 +28416,7 @@
       <c r="A467" t="s">
         <v>928</v>
       </c>
-      <c r="B467" s="7" t="str">
+      <c r="B467" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -28404,7 +28440,7 @@
       <c r="A468" t="s">
         <v>930</v>
       </c>
-      <c r="B468" s="7" t="str">
+      <c r="B468" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -28428,7 +28464,7 @@
       <c r="A469" t="s">
         <v>932</v>
       </c>
-      <c r="B469" s="7" t="str">
+      <c r="B469" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -28449,7 +28485,7 @@
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B470" s="7" t="str">
+      <c r="B470" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -28476,7 +28512,7 @@
       <c r="A471" t="s">
         <v>935</v>
       </c>
-      <c r="B471" s="7" t="str">
+      <c r="B471" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -28500,7 +28536,7 @@
       <c r="A472" t="s">
         <v>937</v>
       </c>
-      <c r="B472" s="7" t="str">
+      <c r="B472" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -28521,7 +28557,7 @@
       <c r="A473" t="s">
         <v>939</v>
       </c>
-      <c r="B473" s="7" t="str">
+      <c r="B473" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -28545,7 +28581,7 @@
       <c r="A474" t="s">
         <v>941</v>
       </c>
-      <c r="B474" s="7" t="str">
+      <c r="B474" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -28569,7 +28605,7 @@
       <c r="A475" t="s">
         <v>943</v>
       </c>
-      <c r="B475" s="7" t="str">
+      <c r="B475" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -28593,7 +28629,7 @@
       <c r="A476" t="s">
         <v>945</v>
       </c>
-      <c r="B476" s="7" t="str">
+      <c r="B476" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -28623,7 +28659,7 @@
       <c r="A477" t="s">
         <v>947</v>
       </c>
-      <c r="B477" s="7" t="str">
+      <c r="B477" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -28653,7 +28689,7 @@
       <c r="A478" t="s">
         <v>949</v>
       </c>
-      <c r="B478" s="7" t="str">
+      <c r="B478" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -28674,7 +28710,7 @@
       <c r="A479" t="s">
         <v>950</v>
       </c>
-      <c r="B479" s="7" t="str">
+      <c r="B479" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -28698,7 +28734,7 @@
       <c r="A480" t="s">
         <v>952</v>
       </c>
-      <c r="B480" s="7" t="str">
+      <c r="B480" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -28722,7 +28758,7 @@
       <c r="A481" t="s">
         <v>954</v>
       </c>
-      <c r="B481" s="7" t="str">
+      <c r="B481" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -28746,7 +28782,7 @@
       <c r="A482" t="s">
         <v>956</v>
       </c>
-      <c r="B482" s="7" t="str">
+      <c r="B482" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -28767,7 +28803,7 @@
       </c>
     </row>
     <row r="483" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B483" s="7" t="str">
+      <c r="B483" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -28791,7 +28827,7 @@
       <c r="A484" t="s">
         <v>959</v>
       </c>
-      <c r="B484" s="7" t="str">
+      <c r="B484" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -28815,7 +28851,7 @@
       <c r="A485" t="s">
         <v>961</v>
       </c>
-      <c r="B485" s="7" t="str">
+      <c r="B485" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -28839,7 +28875,7 @@
       <c r="A486" t="s">
         <v>963</v>
       </c>
-      <c r="B486" s="7" t="str">
+      <c r="B486" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -28869,7 +28905,7 @@
       <c r="A487" t="s">
         <v>965</v>
       </c>
-      <c r="B487" s="7" t="str">
+      <c r="B487" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -28893,7 +28929,7 @@
       <c r="A488" t="s">
         <v>967</v>
       </c>
-      <c r="B488" s="7" t="str">
+      <c r="B488" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -28917,7 +28953,7 @@
       <c r="A489" t="s">
         <v>969</v>
       </c>
-      <c r="B489" s="7" t="str">
+      <c r="B489" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -28941,7 +28977,7 @@
       <c r="A490" t="s">
         <v>971</v>
       </c>
-      <c r="B490" s="7" t="str">
+      <c r="B490" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -28971,7 +29007,7 @@
       <c r="A491" t="s">
         <v>973</v>
       </c>
-      <c r="B491" s="7" t="str">
+      <c r="B491" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -28995,7 +29031,7 @@
       <c r="A492" t="s">
         <v>975</v>
       </c>
-      <c r="B492" s="7" t="str">
+      <c r="B492" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -29013,7 +29049,7 @@
       <c r="A493" t="s">
         <v>976</v>
       </c>
-      <c r="B493" s="7" t="str">
+      <c r="B493" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -29037,7 +29073,7 @@
       <c r="A494" t="s">
         <v>978</v>
       </c>
-      <c r="B494" s="7" t="str">
+      <c r="B494" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -29067,7 +29103,7 @@
       <c r="A495" t="s">
         <v>980</v>
       </c>
-      <c r="B495" s="7" t="str">
+      <c r="B495" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -29085,7 +29121,7 @@
       </c>
     </row>
     <row r="496" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B496" s="7" t="str">
+      <c r="B496" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -29106,7 +29142,7 @@
       <c r="A497" t="s">
         <v>983</v>
       </c>
-      <c r="B497" s="7" t="str">
+      <c r="B497" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -29130,7 +29166,7 @@
       <c r="A498" t="s">
         <v>985</v>
       </c>
-      <c r="B498" s="7" t="str">
+      <c r="B498" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -29151,7 +29187,7 @@
       <c r="A499" t="s">
         <v>987</v>
       </c>
-      <c r="B499" s="7" t="str">
+      <c r="B499" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -29175,7 +29211,7 @@
       <c r="A500" t="s">
         <v>989</v>
       </c>
-      <c r="B500" s="7" t="str">
+      <c r="B500" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -29199,7 +29235,7 @@
       <c r="A501" t="s">
         <v>991</v>
       </c>
-      <c r="B501" s="7" t="str">
+      <c r="B501" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -29223,7 +29259,7 @@
       <c r="A502" t="s">
         <v>993</v>
       </c>
-      <c r="B502" s="7" t="str">
+      <c r="B502" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -29244,7 +29280,7 @@
       <c r="A503" t="s">
         <v>995</v>
       </c>
-      <c r="B503" s="7" t="str">
+      <c r="B503" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -29274,7 +29310,7 @@
       <c r="A504" t="s">
         <v>997</v>
       </c>
-      <c r="B504" s="7" t="str">
+      <c r="B504" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -29304,7 +29340,7 @@
       <c r="A505" t="s">
         <v>999</v>
       </c>
-      <c r="B505" s="7" t="str">
+      <c r="B505" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -29325,7 +29361,7 @@
       <c r="A506" t="s">
         <v>1001</v>
       </c>
-      <c r="B506" s="7" t="str">
+      <c r="B506" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -29346,7 +29382,7 @@
       <c r="A507" t="s">
         <v>1002</v>
       </c>
-      <c r="B507" s="7" t="str">
+      <c r="B507" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -29376,7 +29412,7 @@
       <c r="A508" t="s">
         <v>1004</v>
       </c>
-      <c r="B508" s="7" t="str">
+      <c r="B508" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -29397,7 +29433,7 @@
       </c>
     </row>
     <row r="509" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B509" s="7" t="str">
+      <c r="B509" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -29421,7 +29457,7 @@
       <c r="A510" t="s">
         <v>1007</v>
       </c>
-      <c r="B510" s="7" t="str">
+      <c r="B510" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Borno</v>
       </c>
@@ -29451,7 +29487,7 @@
       <c r="A511" t="s">
         <v>1009</v>
       </c>
-      <c r="B511" s="7" t="str">
+      <c r="B511" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -29481,7 +29517,7 @@
       <c r="A512" t="s">
         <v>1011</v>
       </c>
-      <c r="B512" s="7" t="str">
+      <c r="B512" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -29499,7 +29535,7 @@
       <c r="A513" t="s">
         <v>1013</v>
       </c>
-      <c r="B513" s="7" t="str">
+      <c r="B513" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -29523,7 +29559,7 @@
       <c r="A514" t="s">
         <v>1015</v>
       </c>
-      <c r="B514" s="7" t="str">
+      <c r="B514" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -29547,7 +29583,7 @@
       <c r="A515" t="s">
         <v>1017</v>
       </c>
-      <c r="B515" s="7" t="str">
+      <c r="B515" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -29577,7 +29613,7 @@
       <c r="A516" t="s">
         <v>1019</v>
       </c>
-      <c r="B516" s="7" t="str">
+      <c r="B516" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -29601,7 +29637,7 @@
       <c r="A517" t="s">
         <v>1021</v>
       </c>
-      <c r="B517" s="7" t="str">
+      <c r="B517" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -29631,7 +29667,7 @@
       <c r="A518" t="s">
         <v>1023</v>
       </c>
-      <c r="B518" s="7" t="str">
+      <c r="B518" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -29655,7 +29691,7 @@
       <c r="A519" t="s">
         <v>1025</v>
       </c>
-      <c r="B519" s="7" t="str">
+      <c r="B519" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kano</v>
       </c>
@@ -29685,7 +29721,7 @@
       <c r="A520" t="s">
         <v>1027</v>
       </c>
-      <c r="B520" s="7" t="str">
+      <c r="B520" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -29706,7 +29742,7 @@
       <c r="A521" t="s">
         <v>1028</v>
       </c>
-      <c r="B521" s="7" t="str">
+      <c r="B521" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -29727,7 +29763,7 @@
       </c>
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B522" s="7" t="str">
+      <c r="B522" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Plateau</v>
       </c>
@@ -29745,7 +29781,7 @@
       <c r="A523" t="s">
         <v>1031</v>
       </c>
-      <c r="B523" s="7" t="str">
+      <c r="B523" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Enugu</v>
       </c>
@@ -29766,7 +29802,7 @@
       <c r="A524" t="s">
         <v>1033</v>
       </c>
-      <c r="B524" s="7" t="str">
+      <c r="B524" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -29793,7 +29829,7 @@
       <c r="A525" t="s">
         <v>1035</v>
       </c>
-      <c r="B525" s="7" t="str">
+      <c r="B525" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Cross River</v>
       </c>
@@ -29814,7 +29850,7 @@
       <c r="A526" t="s">
         <v>1037</v>
       </c>
-      <c r="B526" s="7" t="str">
+      <c r="B526" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Benue</v>
       </c>
@@ -29838,7 +29874,7 @@
       <c r="A527" t="s">
         <v>1039</v>
       </c>
-      <c r="B527" s="7" t="str">
+      <c r="B527" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -29862,7 +29898,7 @@
       <c r="A528" t="s">
         <v>1041</v>
       </c>
-      <c r="B528" s="7" t="str">
+      <c r="B528" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -29886,7 +29922,7 @@
       <c r="A529" t="s">
         <v>1043</v>
       </c>
-      <c r="B529" s="7" t="str">
+      <c r="B529" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Lagos</v>
       </c>
@@ -29916,7 +29952,7 @@
       <c r="A530" t="s">
         <v>1045</v>
       </c>
-      <c r="B530" s="7" t="str">
+      <c r="B530" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -29943,7 +29979,7 @@
       <c r="A531" t="s">
         <v>1047</v>
       </c>
-      <c r="B531" s="7" t="str">
+      <c r="B531" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -29964,7 +30000,7 @@
       <c r="A532" t="s">
         <v>1049</v>
       </c>
-      <c r="B532" s="7" t="str">
+      <c r="B532" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -29982,7 +30018,7 @@
       <c r="A533" t="s">
         <v>1051</v>
       </c>
-      <c r="B533" s="7" t="str">
+      <c r="B533" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Kaduna</v>
       </c>
@@ -30006,7 +30042,7 @@
       <c r="A534" t="s">
         <v>1053</v>
       </c>
-      <c r="B534" s="7" t="str">
+      <c r="B534" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -30024,7 +30060,7 @@
       </c>
     </row>
     <row r="535" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B535" s="7" t="str">
+      <c r="B535" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -30048,7 +30084,7 @@
       <c r="A536" t="s">
         <v>1055</v>
       </c>
-      <c r="B536" s="7" t="str">
+      <c r="B536" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Abuja</v>
       </c>
@@ -30072,7 +30108,7 @@
       <c r="A537" t="s">
         <v>1057</v>
       </c>
-      <c r="B537" s="7" t="str">
+      <c r="B537" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -30096,7 +30132,7 @@
       <c r="A538" t="s">
         <v>1059</v>
       </c>
-      <c r="B538" s="7" t="str">
+      <c r="B538" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Delta</v>
       </c>
@@ -30120,7 +30156,7 @@
       <c r="A539" t="s">
         <v>1061</v>
       </c>
-      <c r="B539" s="7" t="str">
+      <c r="B539" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Rivers</v>
       </c>
@@ -30150,7 +30186,7 @@
       <c r="A540" t="s">
         <v>1063</v>
       </c>
-      <c r="B540" s="7" t="str">
+      <c r="B540" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -30174,7 +30210,7 @@
       <c r="A541" t="s">
         <v>1065</v>
       </c>
-      <c r="B541" s="7" t="str">
+      <c r="B541" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Oyo</v>
       </c>
@@ -30198,7 +30234,7 @@
       <c r="A542" t="s">
         <v>1067</v>
       </c>
-      <c r="B542" s="7" t="str">
+      <c r="B542" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -30219,7 +30255,7 @@
       <c r="A543" t="s">
         <v>1069</v>
       </c>
-      <c r="B543" s="7" t="str">
+      <c r="B543" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -30246,7 +30282,7 @@
       <c r="A544" t="s">
         <v>1071</v>
       </c>
-      <c r="B544" s="7" t="str">
+      <c r="B544" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -30270,7 +30306,7 @@
       <c r="A545" t="s">
         <v>1073</v>
       </c>
-      <c r="B545" s="7" t="str">
+      <c r="B545" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -30291,7 +30327,7 @@
       <c r="A546" t="s">
         <v>1075</v>
       </c>
-      <c r="B546" s="7" t="str">
+      <c r="B546" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Sokoto</v>
       </c>
@@ -30321,7 +30357,7 @@
       <c r="A547" t="s">
         <v>1077</v>
       </c>
-      <c r="B547" s="7" t="str">
+      <c r="B547" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Ekiti</v>
       </c>
@@ -30348,7 +30384,7 @@
       </c>
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B548" s="7" t="str">
+      <c r="B548" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Katsina</v>
       </c>
@@ -30369,7 +30405,7 @@
       <c r="A549" t="s">
         <v>1079</v>
       </c>
-      <c r="B549" s="7" t="str">
+      <c r="B549" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Bauchi</v>
       </c>
@@ -30393,7 +30429,7 @@
       <c r="A550" t="s">
         <v>1081</v>
       </c>
-      <c r="B550" s="7" t="str">
+      <c r="B550" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Niger</v>
       </c>
@@ -30417,7 +30453,7 @@
       <c r="A551" t="s">
         <v>1083</v>
       </c>
-      <c r="B551" s="7" t="str">
+      <c r="B551" s="3" t="str">
         <f ca="1">PROPER(TRIM(Table1[[#This Row],[State]]))</f>
         <v>Imo</v>
       </c>
@@ -30455,7 +30491,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EA3F68-4AF1-4C2A-9479-4465B8321795}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -30463,81 +30499,115 @@
     <col min="3" max="3" width="21.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
         <v>1085</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1086</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>1087</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="9">
         <v>43</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="9">
         <v>395</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="G3" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="116" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="9">
         <v>55</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+      <c r="G4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="9">
         <v>413</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="8" t="s">
         <v>1090</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="9">
         <v>106</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="8" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="9">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="8" t="s">
         <v>1088</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>1</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
